--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20260107_201442.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20260107_201442.xlsx
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
